--- a/WS/WS_annotations_scores.xlsx
+++ b/WS/WS_annotations_scores.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ku51015\CHMURA\mystuff\Graph-Vizualisation-Rating-Metric-randoms\WS\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3B51BB-B82F-4EAF-925A-C3C0DDCE7C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="4190" yWindow="440" windowWidth="25800" windowHeight="5740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4185" yWindow="435" windowWidth="25800" windowHeight="5745"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -51,8 +45,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,7 +79,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -143,7 +137,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -195,7 +189,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -389,24 +383,24 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.81640625" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -429,7 +423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -452,7 +446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -475,7 +469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>2</v>
       </c>
@@ -498,7 +492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -521,7 +515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -544,7 +538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -567,7 +561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -590,7 +584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -613,7 +607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -636,7 +630,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
@@ -657,6 +651,151 @@
       </c>
       <c r="G11">
         <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/WS/WS_annotations_scores.xlsx
+++ b/WS/WS_annotations_scores.xlsx
@@ -383,7 +383,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -768,34 +768,142 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>20</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
